--- a/salon_forms/012_microneedling_consultation_form--salon_forms.xlsx
+++ b/salon_forms/012_microneedling_consultation_form--salon_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1260,8 +1260,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'normal_skin'}</t>
+          <t>normal_skin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Normal Skin'}</t>
+          <t>Normal Skin</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'dry_skin'}</t>
+          <t>dry_skin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Dry Skin'}</t>
+          <t>Dry Skin</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'oily_skin'}</t>
+          <t>oily_skin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Oily Skin'}</t>
+          <t>Oily Skin</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'combination_skin'}</t>
+          <t>combination_skin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Combination Skin'}</t>
+          <t>Combination Skin</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'sensitive_skin'}</t>
+          <t>sensitive_skin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Sensitive Skin'}</t>
+          <t>Sensitive Skin</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'acne_prone_skin'}</t>
+          <t>acne_prone_skin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Acne Prone Skin'}</t>
+          <t>Acne Prone Skin</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1884,12 +1884,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -2037,12 +2037,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -2122,12 +2122,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -2241,12 +2241,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -2428,12 +2428,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2615,12 +2615,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -2649,12 +2649,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2700,12 +2700,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2717,12 +2717,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -2734,12 +2734,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2785,12 +2785,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -2938,12 +2938,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -2955,12 +2955,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -3040,12 +3040,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -3057,12 +3057,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3091,12 +3091,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3108,12 +3108,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -3142,12 +3142,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -3159,12 +3159,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3210,12 +3210,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -3261,12 +3261,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3278,12 +3278,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3295,12 +3295,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3380,12 +3380,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3397,12 +3397,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3516,12 +3516,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3635,12 +3635,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -3652,12 +3652,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -3669,12 +3669,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3720,12 +3720,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3754,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -3771,12 +3771,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3788,12 +3788,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3856,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3890,12 +3890,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3907,12 +3907,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>{'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>{'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -3958,12 +3958,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
